--- a/data/trans_orig/Q5411-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q5411-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14138</t>
+          <t>12778</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>6835</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20920</t>
+          <t>20664</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11435</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28007</t>
+          <t>29310</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>278445</t>
+          <t>279805</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289783</t>
+          <t>289727</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>322014</t>
+          <t>322270</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>336113</t>
+          <t>336099</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>607510</t>
+          <t>606207</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>624082</t>
+          <t>623864</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13913</t>
+          <t>14624</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30641</t>
+          <t>31822</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>38289</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66693</t>
+          <t>66361</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57891</t>
+          <t>58323</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>90461</t>
+          <t>91752</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179242</t>
+          <t>178061</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>195970</t>
+          <t>195259</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>267215</t>
+          <t>267547</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>295214</t>
+          <t>295619</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>453330</t>
+          <t>452039</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>485900</t>
+          <t>485468</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,27%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19840</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39127</t>
+          <t>39294</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50278</t>
+          <t>49473</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82118</t>
+          <t>82329</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74520</t>
+          <t>73744</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111553</t>
+          <t>110795</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>463339</t>
+          <t>463172</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>482626</t>
+          <t>481695</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>594724</t>
+          <t>594513</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>626564</t>
+          <t>627369</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1067755</t>
+          <t>1068513</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1104788</t>
+          <t>1105564</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -1992,12 +1992,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10373</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27643</t>
+          <t>28229</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2007,12 +2007,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16376</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36207</t>
+          <t>36843</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31799</t>
+          <t>31143</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55166</t>
+          <t>57673</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>282143</t>
+          <t>281557</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>299413</t>
+          <t>299468</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>317789</t>
+          <t>317153</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>337620</t>
+          <t>337330</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>608616</t>
+          <t>606109</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>631983</t>
+          <t>632639</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32346</t>
+          <t>31735</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58812</t>
+          <t>58349</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>119745</t>
+          <t>119351</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>158688</t>
+          <t>159705</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>157592</t>
+          <t>158029</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>206240</t>
+          <t>209026</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,72%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>191039</t>
+          <t>191502</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>217505</t>
+          <t>218116</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>230291</t>
+          <t>229274</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>269234</t>
+          <t>269628</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>432590</t>
+          <t>429804</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>481238</t>
+          <t>480801</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,26%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44951</t>
+          <t>46468</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77478</t>
+          <t>78774</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>141800</t>
+          <t>140867</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>188729</t>
+          <t>186359</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>197047</t>
+          <t>196079</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>255925</t>
+          <t>251238</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>482159</t>
+          <t>480863</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>514686</t>
+          <t>513169</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>554246</t>
+          <t>556616</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>601175</t>
+          <t>602108</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1046687</t>
+          <t>1051374</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1105565</t>
+          <t>1106533</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,95%</t>
         </is>
       </c>
     </row>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7693</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22465</t>
+          <t>22173</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8932</t>
+          <t>8505</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24986</t>
+          <t>23909</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19113</t>
+          <t>20421</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41752</t>
+          <t>40943</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>311865</t>
+          <t>312157</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>326637</t>
+          <t>326444</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>352776</t>
+          <t>353853</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>368830</t>
+          <t>369257</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>670340</t>
+          <t>671149</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>692979</t>
+          <t>691671</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -3594,12 +3594,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25231</t>
+          <t>24829</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44960</t>
+          <t>45034</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69530</t>
+          <t>69667</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108784</t>
+          <t>106082</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>101316</t>
+          <t>102134</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>144485</t>
+          <t>144637</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3679,12 +3679,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>212038</t>
+          <t>211964</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>231767</t>
+          <t>232169</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>291385</t>
+          <t>294087</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>330639</t>
+          <t>330502</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>512682</t>
+          <t>512530</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>555851</t>
+          <t>555033</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,46%</t>
         </is>
       </c>
     </row>
@@ -3937,12 +3937,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35881</t>
+          <t>36871</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60862</t>
+          <t>60684</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>84091</t>
+          <t>83197</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>126267</t>
+          <t>124541</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>126324</t>
+          <t>127556</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>174546</t>
+          <t>176448</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4022,12 +4022,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>530466</t>
+          <t>530644</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>555447</t>
+          <t>554457</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>651664</t>
+          <t>653390</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>693840</t>
+          <t>694734</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1194713</t>
+          <t>1192811</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1242935</t>
+          <t>1241703</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,68%</t>
         </is>
       </c>
     </row>
@@ -4505,32 +4505,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9876</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5779</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15613</t>
+          <t>16371</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14669</t>
+          <t>16632</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4780</t>
+          <t>11809</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24831</t>
+          <t>23656</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4575,32 +4575,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>24545</t>
+          <t>26951</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11460</t>
+          <t>20241</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35202</t>
+          <t>35597</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -4618,32 +4618,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>358289</t>
+          <t>396761</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>352552</t>
+          <t>390709</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>362386</t>
+          <t>401323</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4653,32 +4653,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>592938</t>
+          <t>421725</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>582776</t>
+          <t>414701</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>602827</t>
+          <t>426548</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4688,32 +4688,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>951228</t>
+          <t>818485</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>940571</t>
+          <t>809839</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>964313</t>
+          <t>825195</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -4731,17 +4731,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4766,17 +4766,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>607607</t>
+          <t>438357</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>607607</t>
+          <t>438357</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>607607</t>
+          <t>438357</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4801,17 +4801,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>975773</t>
+          <t>845436</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>975773</t>
+          <t>845436</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>975773</t>
+          <t>845436</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4848,32 +4848,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39775</t>
+          <t>42660</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31499</t>
+          <t>33980</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51286</t>
+          <t>54180</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>105604</t>
+          <t>113223</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92769</t>
+          <t>99455</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>117541</t>
+          <t>126648</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4918,32 +4918,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>145379</t>
+          <t>155883</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>130344</t>
+          <t>139560</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>162241</t>
+          <t>173482</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,43%</t>
         </is>
       </c>
     </row>
@@ -4961,32 +4961,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>242238</t>
+          <t>266652</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>230727</t>
+          <t>255132</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>250514</t>
+          <t>275332</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4996,32 +4996,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>319627</t>
+          <t>350739</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>307690</t>
+          <t>337314</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>332462</t>
+          <t>364507</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5031,32 +5031,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>561865</t>
+          <t>617391</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>545003</t>
+          <t>599792</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>576900</t>
+          <t>633714</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,95%</t>
         </is>
       </c>
     </row>
@@ -5074,17 +5074,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5109,17 +5109,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>425231</t>
+          <t>463962</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>425231</t>
+          <t>463962</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>425231</t>
+          <t>463962</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5144,17 +5144,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>707244</t>
+          <t>773274</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>707244</t>
+          <t>773274</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>707244</t>
+          <t>773274</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>49651</t>
+          <t>52979</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39462</t>
+          <t>42471</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61756</t>
+          <t>67575</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>120272</t>
+          <t>129855</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68918</t>
+          <t>115502</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>156864</t>
+          <t>146572</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5261,32 +5261,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>169923</t>
+          <t>182834</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>110236</t>
+          <t>164800</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>201182</t>
+          <t>204185</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -5304,32 +5304,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>600527</t>
+          <t>663412</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>588422</t>
+          <t>648816</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>610716</t>
+          <t>673920</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>912566</t>
+          <t>772464</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>875974</t>
+          <t>755747</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>963920</t>
+          <t>786817</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5374,32 +5374,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1513093</t>
+          <t>1435876</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1481834</t>
+          <t>1414525</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1572780</t>
+          <t>1453910</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>89,82%</t>
         </is>
       </c>
     </row>
@@ -5417,17 +5417,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1032838</t>
+          <t>902319</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1032838</t>
+          <t>902319</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1032838</t>
+          <t>902319</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5487,17 +5487,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1683016</t>
+          <t>1618710</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1683016</t>
+          <t>1618710</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1683016</t>
+          <t>1618710</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
